--- a/insurance_forms/042_travel_insurance_decline_form--insurance_forms.xlsx
+++ b/insurance_forms/042_travel_insurance_decline_form--insurance_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Decline Reason</t>
+          <t>Reason for Declining Travel Insurance?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Provide More Details</t>
+          <t>Can you provide more details?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_3</t>
+          <t>main_reason_decline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reason for Decline</t>
+          <t>Main Reason for Decline?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_4</t>
+          <t>additional_info_decline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reason for Decline</t>
+          <t>Additional Info</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_5</t>
+          <t>confirm_decline_reason</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Confirm Decline Reason</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_6</t>
+          <t>other_reason_decline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Decline Reason</t>
+          <t>Other Reason(s) for Decline?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,18 +648,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_7</t>
+          <t>more_details_decline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reason for Decline</t>
+          <t>More Details about Decline</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_8</t>
+          <t>other_info_decline</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Info</t>
+          <t>More Info about Decline</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_9</t>
+          <t>confirm_decline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Decline Reason</t>
+          <t>Is this correct?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_10</t>
+          <t>final_decline_reason</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reason for Decline</t>
+          <t>Final Reason for Decline</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,18 +740,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_11</t>
+          <t>last_reason_decline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>More Info</t>
+          <t>Last Reason for Decline</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,18 +763,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>travel_insurance_decline_form_page_12</t>
+          <t>final_info_decline</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Decline Reason</t>
+          <t>Last Info about Decline</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
